--- a/AAII_Financials/Quarterly/HCMLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCMLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="92">
   <si>
     <t>HCMLY</t>
   </si>
@@ -656,174 +656,182 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -866,83 +874,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>8997800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16611300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7248200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16168000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8047200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>13463400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5564600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>12918000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6436300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>11441300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5734500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14872000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7977200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>13892600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>6591100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>15630400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>7634500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>13620700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>5983200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>6975400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>12976400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>5655400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>6757800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>7285900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>7538600</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -988,80 +1002,86 @@
       <c r="Q9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="3">
         <v>9899300</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V9" s="3">
         <v>9115600</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X9" s="3">
         <v>7771800</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="3">
         <v>7100800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="3">
         <v>7072600</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD9" s="3">
         <v>8352000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF9" s="3">
         <v>8256400</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH9" s="3">
         <v>8758900</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>8064400</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL9" s="3">
         <v>3685600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>7670500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>3545000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>3933900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>3975400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>4123400</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1107,80 +1127,86 @@
       <c r="Q10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="3">
         <v>6711900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>7052400</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X10" s="3">
         <v>5691600</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3">
         <v>5817200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="3">
         <v>4368700</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="3">
         <v>6520100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF10" s="3">
         <v>5636200</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH10" s="3">
         <v>6871500</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>5556200</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL10" s="3">
         <v>3289800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>5305900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>2110500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>2823900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>3310600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>3415100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,8 +1248,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1341,8 +1369,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,8 +1494,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1507,80 +1547,86 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>103000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>246900</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-20400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>22800</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>8600</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>23900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-240400</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>187200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>334600</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>69300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>-217000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>-364600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>-320000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>-454600</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AQ14" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1623,11 +1669,11 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1698,8 +1744,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,8 +1790,10 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1785,80 +1839,86 @@
       <c r="Q17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T17" s="3">
         <v>14375500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="3">
         <v>13462700</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X17" s="3">
         <v>11519400</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3">
         <v>10485700</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="3">
         <v>10374500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD17" s="3">
         <v>12444700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF17" s="3">
         <v>11894700</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH17" s="3">
         <v>13164800</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>12541000</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL17" s="3">
         <v>5995000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>11131100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>5134100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>5803100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>5700500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>6481300</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1904,80 +1964,86 @@
       <c r="Q18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T18" s="3">
         <v>2235800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3">
         <v>2705200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="3">
         <v>1944000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3">
         <v>2432300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1066800</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="3">
         <v>2427300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1997900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH18" s="3">
         <v>2465600</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>1079600</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL18" s="3">
         <v>980400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>1845300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>521300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>954700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>1585400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>1057300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,8 +2085,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2066,80 +2134,86 @@
       <c r="Q20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="3">
         <v>6800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3">
         <v>-14700</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X20" s="3">
         <v>-152300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-75700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-109100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-94700</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-97900</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-110100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-99500</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-138600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>475100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>12100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-113900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>90100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2191,74 +2265,80 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>5336900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>4966300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>3784700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3">
         <v>3203200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>3592100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>2115100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL21" s="3">
         <v>1423400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>3455500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1084900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1598800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>2229500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>1738600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2304,80 +2384,86 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>232000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>217400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>226200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>209600</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>262100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>307000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
         <v>348900</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3">
         <v>384300</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>379700</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL22" s="3">
         <v>182800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>737300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>190900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>223700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>221600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>239200</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2423,80 +2509,86 @@
       <c r="Q23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="3">
         <v>2010600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V23" s="3">
         <v>2473100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X23" s="3">
         <v>1565500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="3">
         <v>2146900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="3">
         <v>695500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD23" s="3">
         <v>2025700</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF23" s="3">
         <v>1551100</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH23" s="3">
         <v>1971100</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>600400</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL23" s="3">
         <v>659000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>1583100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>342500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>617200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>1453900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>887400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2542,80 +2634,86 @@
       <c r="Q24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="3">
         <v>537500</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V24" s="3">
         <v>650000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X24" s="3">
         <v>417100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="3">
         <v>533400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB24" s="3">
         <v>217200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="3">
         <v>518100</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF24" s="3">
         <v>351100</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH24" s="3">
         <v>512100</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>196000</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL24" s="3">
         <v>185800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>423900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>79400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>63200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>323100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>387300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,8 +2831,14 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2780,80 +2884,86 @@
       <c r="Q26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T26" s="3">
         <v>1473200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V26" s="3">
         <v>1823100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X26" s="3">
         <v>1148400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1613600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB26" s="3">
         <v>478300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD26" s="3">
         <v>1507600</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF26" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH26" s="3">
         <v>1459100</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>404400</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL26" s="3">
         <v>473100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>1159200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>263200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>554000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>1130800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>500200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2899,80 +3009,86 @@
       <c r="Q27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T27" s="3">
         <v>1298900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V27" s="3">
         <v>1641900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X27" s="3">
         <v>890000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1391500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB27" s="3">
         <v>361700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD27" s="3">
         <v>1337800</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF27" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH27" s="3">
         <v>1303800</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>326400</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL27" s="3">
         <v>435000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>1017600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>227000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>469100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>1070700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>399700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3206,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3134,11 +3256,11 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3185,17 +3307,17 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL29" s="3">
         <v>0</v>
@@ -3204,13 +3326,19 @@
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>11400</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AQ29" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3456,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,8 +3581,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3494,80 +3634,86 @@
       <c r="Q32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T32" s="3">
         <v>-6800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V32" s="3">
         <v>14700</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X32" s="3">
         <v>152300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z32" s="3">
         <v>75700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB32" s="3">
         <v>109100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD32" s="3">
         <v>94700</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF32" s="3">
         <v>97900</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH32" s="3">
         <v>110100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>99500</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL32" s="3">
         <v>138600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-475100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-12100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>113900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-90100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-69400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3613,80 +3759,86 @@
       <c r="Q33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T33" s="3">
         <v>1298900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V33" s="3">
         <v>1641900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X33" s="3">
         <v>890000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1391500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB33" s="3">
         <v>361700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD33" s="3">
         <v>1337800</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF33" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH33" s="3">
         <v>1303800</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>326400</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL33" s="3">
         <v>435000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>1017600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>227000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>469100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>1082100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,8 +3956,14 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3851,204 +4009,216 @@
       <c r="Q35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T35" s="3">
         <v>1298900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V35" s="3">
         <v>1641900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X35" s="3">
         <v>890000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1391500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB35" s="3">
         <v>361700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD35" s="3">
         <v>1337800</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF35" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH35" s="3">
         <v>1303800</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>326400</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL35" s="3">
         <v>435000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>1017600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>227000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>469100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>1082100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4260,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,56 +4305,58 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4457900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4490600</v>
+      </c>
+      <c r="F41" s="3">
         <v>6860500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6822300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5325200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4791000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5900600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6330000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3883800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3869000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7222800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6650700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4083300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4003900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>10624300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4210,98 +4384,104 @@
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4515100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF41" s="3">
         <v>3239400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3">
         <v>2769500</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>2530800</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL41" s="3">
         <v>4313400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>3619300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>4260200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>8386700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>4751000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>4061300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>3800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>3800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>5900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>6500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -4353,74 +4533,80 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK42" s="3" t="s">
-        <v>8</v>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
       </c>
       <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO42" s="3">
         <v>1809100</v>
       </c>
-      <c r="AN42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3292100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3316200</v>
+      </c>
+      <c r="F43" s="3">
         <v>2817300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2801700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2985100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2685700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3542300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3800100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4374600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4357900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3945100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3632600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4620800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4530900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3647800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4448,98 +4634,104 @@
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD43" s="3">
         <v>3260000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF43" s="3">
         <v>4113800</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3">
         <v>3754000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>4392400</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL43" s="3">
         <v>4344500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>3974900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>3208400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>3140700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>4017800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>4137900</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2571800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2590600</v>
+      </c>
+      <c r="F44" s="3">
         <v>2164100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2152000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2174100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1956000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3439700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3690000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3525500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3512000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3333500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3069500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3464200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3396800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3093000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4567,98 +4759,104 @@
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="3">
         <v>2714700</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="3">
         <v>3108500</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3">
         <v>3392800</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>3335400</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL44" s="3">
         <v>2874900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>2831700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>2759400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>2739000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>2921200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>3002000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>148400</v>
+      </c>
+      <c r="F45" s="3">
         <v>303900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>302200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>227600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>204800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>281400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>301900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>130200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>129700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>494000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>454900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>263700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>258600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>539700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4686,98 +4884,104 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>2800700</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>2780900</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>2921500</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1469600</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL45" s="3">
         <v>2406800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>2947300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>3157200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>3970200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>3333300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>4453800</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11375000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11458400</v>
+      </c>
+      <c r="F46" s="3">
         <v>12365200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12296500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11554400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10395400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13448800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14427400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12876700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12827400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>15250700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>14042800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13518300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13255200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18151300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4805,98 +5009,104 @@
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD46" s="3">
         <v>13290500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="3">
         <v>13242600</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH46" s="3">
         <v>12837800</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>11728200</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL46" s="3">
         <v>13939700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>13373200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>13385200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>14947700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>15023300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>15655000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4389900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4422000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4065800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>4043200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>4357000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3919900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>3895500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>4178900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>4162000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>4146100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>4080500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3757300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>4168200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4087100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3743000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4924,98 +5134,104 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4820900</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="3">
         <v>4638300</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3">
         <v>4673500</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>4359600</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL47" s="3">
         <v>4581600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>4414900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>4559500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>5528600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>4521100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>4770600</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16930700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17054800</v>
+      </c>
+      <c r="F48" s="3">
         <v>15800500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>15712700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>15752900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14172700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22409500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>24040200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>22613000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>22526500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>22968700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21149500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>22880700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>22435400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>22014300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5043,98 +5259,104 @@
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>29595000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>29344700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>30712500</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>30116900</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL48" s="3">
         <v>31511800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>30982400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>32161700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>33190500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>34249800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>35057500</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11233900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11316300</v>
+      </c>
+      <c r="F49" s="3">
         <v>8957700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8907900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8971700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8071700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>18731400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>20094500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>18670200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>18598700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>18663800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>17185500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>18562700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>18201400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>16702200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5162,50 +5384,56 @@
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD49" s="3">
         <v>14893800</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF49" s="3">
         <v>14718100</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3">
         <v>16358300</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>15661900</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL49" s="3">
         <v>17306900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>16935200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>17258700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>35754400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>17816100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>18146500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5551,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,56 +5676,62 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>278000</v>
+      </c>
+      <c r="F52" s="3">
         <v>460300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>457700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>291700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>262500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>744900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>799100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>318300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>317100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>764800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>704200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>534200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>523800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>972200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5519,50 +5759,56 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD52" s="3">
         <v>869700</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1053200</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1154100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1421400</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>1297800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>1374200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>2165300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1797700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>1970600</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,56 +5926,62 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44884900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>45213900</v>
+      </c>
+      <c r="F54" s="3">
         <v>42379700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>42144300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>41501100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>37338100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>59905300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>64264700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>59452500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>59225100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>62568000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>57612400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>60321200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>59147300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>62295700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5757,50 +6009,56 @@
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD54" s="3">
         <v>63469900</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="3">
         <v>62996800</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3">
         <v>65736100</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>63288000</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL54" s="3">
         <v>68712200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>67003500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>68739300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>72089800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>72820900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>74201200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +6100,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,56 +6145,58 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4290800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4322300</v>
+      </c>
+      <c r="F57" s="3">
         <v>4023000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4000600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3928200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3534100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4830200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5181700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4870900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4852300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4827400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4445100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4805200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4711700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>4318300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5962,98 +6224,104 @@
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD57" s="3">
         <v>3847800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="3">
         <v>3742600</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3">
         <v>4151500</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>4068100</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL57" s="3">
         <v>3385200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>3233500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>3209400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>3424500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>3507300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>3651200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3008700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3030700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1740300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1730700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>924200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>831500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2032700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2180600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2280200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2271500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1681600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1548400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1156600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1134100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1789800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6081,98 +6349,104 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD58" s="3">
         <v>2273900</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="3">
         <v>3044700</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3">
         <v>3373000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>5019500</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL58" s="3">
         <v>4774500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>4914100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>4773500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>5152700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>5831000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>7076700</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3163400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3186600</v>
+      </c>
+      <c r="F59" s="3">
         <v>3572700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3552900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2923500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2630200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3901000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4184900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3321800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3309100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4065000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3743100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3186000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3124000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3470400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6200,98 +6474,104 @@
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD59" s="3">
         <v>3831500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3671300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3">
         <v>4288100</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>3480100</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL59" s="3">
         <v>3876400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>3811100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>3726800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>4376100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>4288100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>4638100</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10462900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10539600</v>
+      </c>
+      <c r="F60" s="3">
         <v>9336000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9284200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7775900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6995900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10763900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11547200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10473000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10432900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10574100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9736600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9147800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8969800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9578600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>8</v>
       </c>
@@ -6319,98 +6599,104 @@
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD60" s="3">
         <v>9953200</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF60" s="3">
         <v>10458500</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH60" s="3">
         <v>11812600</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>12567700</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL60" s="3">
         <v>12036200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>11958800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>11709700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>12953300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>13626400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>15366100</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10545800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10623100</v>
+      </c>
+      <c r="F61" s="3">
         <v>9921200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9866100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11416100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10270900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>13257900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>14222600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13744700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>13692100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15040500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>13849200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>15441500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>15141000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>15654200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6439,97 +6725,103 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>13281800</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>13708500</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>14382800</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>14169700</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>15227500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>14603700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>14598700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>15267700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>16049500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>15822700</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1412100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1422500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1418800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1410900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1441000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1296500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2229100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2391400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2190100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2181700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2231400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2054700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2088600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2047900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2072100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6557,50 +6849,56 @@
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD62" s="3">
         <v>5948600</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3">
         <v>6052100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
         <v>6446400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>6265400</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="3">
         <v>7178300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>7106000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>7406300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>7887600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>8226200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>8129900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +7016,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +7141,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,56 +7266,62 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24233900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>24411600</v>
+      </c>
+      <c r="F66" s="3">
         <v>22094700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21972000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>22243700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>20012400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>29056000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>31170500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>29337900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>29225700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>30761500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>28325100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>29804700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>29224600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>30269200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
@@ -7033,50 +7349,56 @@
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD66" s="3">
         <v>32376000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF66" s="3">
         <v>33284000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3">
         <v>36086300</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>36129800</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL66" s="3">
         <v>38263200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>37530900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>37688600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>40173000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>42012100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>43742400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7440,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7561,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7686,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7811,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,8 +7936,14 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7671,50 +8019,56 @@
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3">
         <v>20867400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
         <v>19781900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>18924100</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>16357700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="3">
         <v>18001000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>17469600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>16706200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>17133700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>16503100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>15518300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8186,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8311,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,56 +8436,62 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19555700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>19699000</v>
+      </c>
+      <c r="F76" s="3">
         <v>19392100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19284400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18411100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16564300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>30059100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>32246600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>29246600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>29134700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>30873100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>28427900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>29539800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>28965000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>31010000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
@@ -8147,50 +8519,56 @@
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD76" s="3">
         <v>31093800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF76" s="3">
         <v>29712800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3">
         <v>29649800</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>27158200</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL76" s="3">
         <v>30449000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>29472600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>31050700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>31916800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>30808800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>30458800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,132 +8686,144 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8479,80 +8869,86 @@
       <c r="Q81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T81" s="3">
         <v>1298900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V81" s="3">
         <v>1641900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X81" s="3">
         <v>890000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1391500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB81" s="3">
         <v>361700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD81" s="3">
         <v>1337800</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF81" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH81" s="3">
         <v>1303800</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>326400</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL81" s="3">
         <v>435000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>1017600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>227000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>469100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>1082100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>415200</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8990,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>340800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>306600</v>
+      </c>
+      <c r="F83" s="3">
         <v>291300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>312500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>303800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>302600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>483300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>445100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>541400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>530900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>500200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>471200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>584400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>605900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>437700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3">
         <v>2646300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2609700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1452000</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1303200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1236600</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1135100</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL83" s="3">
         <v>581600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>1135100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>551500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>758000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>554000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>612000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9236,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9361,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9486,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9611,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9736,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>352800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1536700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1528100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>220700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>198500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2573400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2760700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>558100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>556000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2695800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2482300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>519600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>509500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1844400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3">
         <v>5712800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="3">
         <v>4792000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD89" s="3">
         <v>4090500</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3">
         <v>1135100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH89" s="3">
         <v>3232000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>54400</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL89" s="3">
         <v>1145200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-138600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-520300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>1842200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>1299600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>543600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9910,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-352700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-355300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-355600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-353700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-312500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-281100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-316200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-339200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-284900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-283800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-460200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-423700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-407900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-399900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-435800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-745000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-504000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1156000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-965500</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-688300</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-908500</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-601400</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-287300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-580600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-342500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-511500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-444200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +10156,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10281,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1703000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1715500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-202400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-201300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1030500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-927100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-727200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-780100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-400100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-398500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-587300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-540700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1385700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1358700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>2511200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
         <v>-5333500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1277400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-923000</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3">
         <v>669100</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1001000</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-489500</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-140600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>109500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>220000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>641000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>444200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,80 +10455,82 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>583500</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>587800</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>1077600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>969500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>880800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>877400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>11900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>10900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>794000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>778500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>8100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1383800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1270100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10073,43 +10541,49 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-342600</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1223300</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-1217500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10701,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10826,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10951,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>194300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>195700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-486800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-484100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>445800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>401000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-734400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-787800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1690400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1683900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-383600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-353200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-2557400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2507600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1213900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3">
         <v>1261500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1962200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1713300</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1123400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-2238700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-1159700</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-412900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1253600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-524400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-1980900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-832600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-628600</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-340800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-306600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-73400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-78700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>85700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>85400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-266600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-245500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-19000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-18600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-57900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-54500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-73800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-76600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V101" s="3">
         <v>73600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-423400</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-189400</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-53200</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-25300</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-108800</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL101" s="3">
         <v>19100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-160700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-32100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-17600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-23800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1149100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1157600</v>
+      </c>
+      <c r="F102" s="3">
         <v>771800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>767500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-704800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-634100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1038400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1114000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1446700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1441200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1458300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1342800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3442400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3375400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3083800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3">
         <v>1714400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
         <v>1129000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3">
         <v>1264800</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3">
         <v>627700</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-1703600</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL102" s="3">
         <v>610700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-1443500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-856900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>484600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>887400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>19700</v>
       </c>
     </row>
